--- a/naver-place-crawler/results_hair/분당_미용실.xlsx
+++ b/naver-place-crawler/results_hair/분당_미용실.xlsx
@@ -421,9 +421,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hair Seed194 수내역점</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>seed194@naver.com</t>
-        </is>
-      </c>
+          <t>미봉헤어 야탑점</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1469-0195</t>
+          <t>0507-1455-7404</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 16 대덕프라자 316호 Hair Seed194</t>
+          <t>경기도 성남시 분당구 성남대로916번길 7 서일빌딩 6층 603호 미봉헤어</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/seed194</t>
+          <t>https://www.instagram.com/mibonghair_yatap</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1765</v>
+        <v>2170</v>
       </c>
       <c r="Q2" t="n">
-        <v>1254</v>
+        <v>1047</v>
       </c>
       <c r="R2" t="n">
-        <v>3019</v>
+        <v>3217</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1993118007</t>
+          <t>1229121617</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1993118007</t>
+          <t>https://m.place.naver.com/place/1229121617</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -658,34 +654,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>오브앤미헤어 서현역점</t>
+          <t>룹헤어 야탑점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thdus10905@naver.com</t>
+          <t>somi_miso@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1345-2089</t>
+          <t>0507-1494-2412</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 326 2층</t>
+          <t>경기도 성남시 분당구 성남대로916번길 7 3층 305호 룹헤어</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ovnme_00</t>
+          <t>https://naver.me/5oExpy79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -711,17 +707,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>8018</v>
+        <v>1438</v>
       </c>
       <c r="Q3" t="n">
-        <v>783</v>
+        <v>657</v>
       </c>
       <c r="R3" t="n">
-        <v>8801</v>
+        <v>2095</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1801434728</t>
+          <t>1146628079</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1801434728</t>
+          <t>https://m.place.naver.com/place/1146628079</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -752,39 +748,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이가자헤어비스 이천일아울렛미금점</t>
+          <t>미봉헤어 서현점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lkjmk2001@naver.com</t>
+          <t>ramdally@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1308-2899</t>
+          <t>0507-1364-9386</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 미금일로154번길 20 2001아울렛 분당점 6층</t>
+          <t>경기도 성남시 분당구 황새울로360번길 26 3층 미봉헤어 서현점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/</t>
+          <t>http://www.instagram.com/mrbonghair_ceo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>5315</v>
+        <v>1625</v>
       </c>
       <c r="Q4" t="n">
-        <v>1875</v>
+        <v>372</v>
       </c>
       <c r="R4" t="n">
-        <v>7190</v>
+        <v>1997</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>30889274</t>
+          <t>446940513</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30889274</t>
+          <t>https://m.place.naver.com/place/446940513</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>준오헤어 서현역3호점</t>
+          <t>아일로헤어</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>junosh33@naver.com</t>
+          <t>julie071117@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>031-706-0605</t>
+          <t>031-708-4089</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 21 산호프라자 2층 준오헤어</t>
+          <t>경기도 성남시 분당구 성남대로926번길 6 야탑 대덕프라자 3층 307호 아일로헤어</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/junosh33</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +874,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +895,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>11430</v>
+        <v>1943</v>
       </c>
       <c r="Q5" t="n">
-        <v>1712</v>
+        <v>843</v>
       </c>
       <c r="R5" t="n">
-        <v>13142</v>
+        <v>2786</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>12820487</t>
+          <t>1493620300</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12820487</t>
+          <t>https://m.place.naver.com/place/1493620300</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -940,34 +936,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에이앤디 분당수내점</t>
+          <t>준오헤어 미금역2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rlagkswnwn2@naver.com</t>
+          <t>mg28817@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1396-6017</t>
+          <t>0507-1372-0609</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 대덕글로리빌딩 2F 206호 에이앤디</t>
+          <t>경기도 성남시 분당구 돌마로 75 미금프라자 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://url.kr/as627v</t>
+          <t>https://blog.naver.com/mg28817</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +984,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1459</v>
+        <v>16674</v>
       </c>
       <c r="Q6" t="n">
-        <v>1830</v>
+        <v>1877</v>
       </c>
       <c r="R6" t="n">
-        <v>3289</v>
+        <v>18551</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1430831536</t>
+          <t>20753530</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430831536</t>
+          <t>https://m.place.naver.com/place/20753530</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브리제헤어 정자역점</t>
+          <t>오뉴월헤어 분당서현점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bidalyong@naver.com</t>
+          <t>toptopq@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1310-8752</t>
+          <t>0507-1415-3447</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 젤존3차 201호</t>
+          <t>경기도 성남시 분당구 황새울로342번길 21 대정빌딩 2층 오뉴월헤어</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brisehair</t>
+          <t>https://blog.naver.com/toptopq</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>10310</v>
+        <v>11738</v>
       </c>
       <c r="Q7" t="n">
-        <v>1407</v>
+        <v>862</v>
       </c>
       <c r="R7" t="n">
-        <v>11717</v>
+        <v>12600</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1171439279</t>
+          <t>1335157831</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1171439279</t>
+          <t>https://m.place.naver.com/place/1335157831</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>꾸밈 미금역점</t>
+          <t>꾸밈 야탑본점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kara0247@naver.com</t>
+          <t>liberoart@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-607-5362</t>
+          <t>0507-1402-0850</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 4층 407호 꾸밈 미금역점</t>
+          <t>경기도 성남시 분당구 성남대로926번길 6 야탑 대덕프라자 304호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ggumim_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1156,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1181,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2097</v>
+        <v>14392</v>
       </c>
       <c r="Q8" t="n">
-        <v>3709</v>
+        <v>2952</v>
       </c>
       <c r="R8" t="n">
-        <v>5806</v>
+        <v>17344</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1487844528</t>
+          <t>36424132</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487844528</t>
+          <t>https://m.place.naver.com/place/36424132</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1218,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>차홍룸 분당점</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>chahong1@naver.com</t>
-        </is>
-      </c>
+          <t>리안헤어 야탑점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1326-6218</t>
+          <t>0507-1488-6767</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 393 두산위브파빌리온 A동 2층 211호</t>
+          <t>경기도 성남시 분당구 장미로92번길 4-4 리안헤어</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chahong1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,12 +1246,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2729</v>
+        <v>2856</v>
       </c>
       <c r="Q9" t="n">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="R9" t="n">
-        <v>2945</v>
+        <v>2955</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2025341850</t>
+          <t>1778006175</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2025341850</t>
+          <t>https://m.place.naver.com/place/1778006175</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>토니앤가이 분당미금역점</t>
+          <t>파우제 맨즈헤어</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dksaledj_@naver.com</t>
+          <t>pausemens@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1365-8540</t>
+          <t>0507-1319-4563</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로171번길 17 1층 105호</t>
+          <t>경기도 성남시 분당구 성남대로916번길 7 402호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/toni_guymigeum?igsh=cTdvc2tlYmFydDFs</t>
+          <t>https://www.instagram.com/pause_yohan</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>6308</v>
+        <v>186</v>
       </c>
       <c r="Q10" t="n">
-        <v>608</v>
+        <v>43</v>
       </c>
       <c r="R10" t="n">
-        <v>6916</v>
+        <v>229</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1716511301</t>
+          <t>2003243884</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716511301</t>
+          <t>https://m.place.naver.com/place/2003243884</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>파우제 야탑점</t>
+          <t>요미앤디 분당정자역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pauseidentity@naver.com</t>
+          <t>rjvhseih@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1496-9307</t>
+          <t>0507-1433-0157</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 203-1호</t>
+          <t>경기도 성남시 분당구 정자일로232번길 25 위브제니스 B동 101호 요미앤디</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pause_identity</t>
+          <t>https://www.instagram.com/yomind_official</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>5237</v>
+        <v>7289</v>
       </c>
       <c r="Q11" t="n">
-        <v>412</v>
+        <v>3164</v>
       </c>
       <c r="R11" t="n">
-        <v>5649</v>
+        <v>10453</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1866672391</t>
+          <t>1783088941</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1866672391</t>
+          <t>https://m.place.naver.com/place/1783088941</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>헤어서보</t>
+          <t>CHOP헤어 분당점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>seobosalon@naver.com</t>
+          <t>chop_bdjj@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1469-7978</t>
+          <t>0507-1424-9636</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로51번길 4-2 1층</t>
+          <t>경기도 성남시 분당구 성남대로 345 305호 CHOP헤어 분당점</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/seobosalon</t>
+          <t>https://www.instagram.com/chop_bundang</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,7 +1533,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1557,17 +1549,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>779</v>
+        <v>6331</v>
       </c>
       <c r="Q12" t="n">
-        <v>136</v>
+        <v>1614</v>
       </c>
       <c r="R12" t="n">
-        <v>915</v>
+        <v>7945</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1701664724</t>
+          <t>1305705196</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701664724</t>
+          <t>https://m.place.naver.com/place/1305705196</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1598,29 +1590,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>꼼나나비앙 판교점</t>
+          <t>더희수뷰티스토리 분당수내점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>comme_pangyo@naver.com</t>
+          <t>ssksh020@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1332-8195</t>
+          <t>0507-1368-7599</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 10 라스트리트 1동 2층 224호</t>
+          <t>경기도 성남시 분당구 수내로 39 지웰푸르지오 2층 239호 더희수뷰티스토리 분당수내역점</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/commenanabien_pangyo/</t>
+          <t>https://www.instagram.com/theheesoobeauty/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1655,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5891</v>
+        <v>3558</v>
       </c>
       <c r="Q13" t="n">
-        <v>362</v>
+        <v>260</v>
       </c>
       <c r="R13" t="n">
-        <v>6253</v>
+        <v>3818</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1867649955</t>
+          <t>1076669006</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867649955</t>
+          <t>https://m.place.naver.com/place/1076669006</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1684,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 동판교H스퀘어점</t>
+          <t>파우제 야탑점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>wodus8449@naver.com</t>
+          <t>pauseidentity@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1439-7713</t>
+          <t>0507-1496-9307</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 235 에이치스퀘어 N동 지하1층 B112호</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 아미고타워 203-1호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pg_no1_master</t>
+          <t>https://www.instagram.com/pause_identity</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1749,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3785</v>
+        <v>5280</v>
       </c>
       <c r="Q14" t="n">
-        <v>833</v>
+        <v>431</v>
       </c>
       <c r="R14" t="n">
-        <v>4618</v>
+        <v>5711</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>21025040</t>
+          <t>1866672391</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21025040</t>
+          <t>https://m.place.naver.com/place/1866672391</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1786,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아이디헤어 정자점</t>
+          <t>준오헤어 서현역3호점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>idjj109@naver.com</t>
+          <t>junosh33@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1476-3308</t>
+          <t>031-706-0605</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 135 정자동 3차 푸르지오시티 D동 2층 215~218호</t>
+          <t>경기도 성남시 분당구 분당로53번길 21 산호프라자 2층 준오헤어</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/idjj109</t>
+          <t>https://blog.naver.com/junosh33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1843,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1639</v>
+        <v>11623</v>
       </c>
       <c r="Q15" t="n">
-        <v>1224</v>
+        <v>1937</v>
       </c>
       <c r="R15" t="n">
-        <v>2863</v>
+        <v>13560</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2087718097</t>
+          <t>12820487</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087718097</t>
+          <t>https://m.place.naver.com/place/12820487</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1880,29 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>준오헤어 서판교점</t>
+          <t>아쎄르</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lowing1018@naver.com</t>
+          <t>hacer_hair@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1332-0610</t>
+          <t>0507-1345-9332</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 249 더제이에스빌딩 2층 준오헤어 서판교점</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 ms프라자 202호 아쎄르 헤어</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/junospg</t>
+          <t>https://blog.naver.com/hacer_hair</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1917,7 +1909,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1937,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>13074</v>
+        <v>1161</v>
       </c>
       <c r="Q16" t="n">
-        <v>476</v>
+        <v>143</v>
       </c>
       <c r="R16" t="n">
-        <v>13550</v>
+        <v>1304</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1391913826</t>
+          <t>1229233683</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391913826</t>
+          <t>https://m.place.naver.com/place/1229233683</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1974,29 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>아이엠헤어 본점</t>
+          <t>맨인무드 분당미금역점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cloud15000@naver.com</t>
+          <t>maninmood@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1344-2326</t>
+          <t>0507-1361-3916</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 16 대덕프라자 2층</t>
+          <t>경기도 성남시 분당구 미금일로90번길 32 2층 204호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cloud15000</t>
+          <t>https://youtube.com/channel/UCM9haZu0TNvj0bTwDu8pMRQ</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2011,7 +2003,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2031,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>9282</v>
+        <v>4186</v>
       </c>
       <c r="Q17" t="n">
-        <v>1011</v>
+        <v>184</v>
       </c>
       <c r="R17" t="n">
-        <v>10293</v>
+        <v>4370</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1701957602</t>
+          <t>1443919723</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701957602</t>
+          <t>https://m.place.naver.com/place/1443919723</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>메이원헤어 미금점</t>
+          <t>아이디헤어 정자점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jjenny87@naver.com</t>
+          <t>idjj109@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1368-0224</t>
+          <t>0507-1476-3308</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 52 MD프라자 2층</t>
+          <t>경기도 성남시 분당구 정자일로 135 정자동 3차 푸르지오시티 D동 2층 215~218호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/may.onehair_mg</t>
+          <t>https://blog.naver.com/idjj109</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2105,7 +2097,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2125,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>6718</v>
+        <v>1694</v>
       </c>
       <c r="Q18" t="n">
-        <v>1818</v>
+        <v>1274</v>
       </c>
       <c r="R18" t="n">
-        <v>8536</v>
+        <v>2968</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1509347542</t>
+          <t>2087718097</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509347542</t>
+          <t>https://m.place.naver.com/place/2087718097</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2162,29 +2154,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>어반트랜드 서현역 본점</t>
+          <t>차홍룸 판교점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ohkong82@naver.com</t>
+          <t>chahong1@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1400-5082</t>
+          <t>0507-1337-4752</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 28 4층 401호, 402호</t>
+          <t>경기도 성남시 분당구 판교역로 136 상가1층 1105호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/urbantrend_hair/</t>
+          <t>https://www.facebook.com/chahongofficial</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2199,7 +2191,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2219,13 +2211,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>22096</v>
+        <v>14136</v>
       </c>
       <c r="Q19" t="n">
-        <v>3018</v>
+        <v>303</v>
       </c>
       <c r="R19" t="n">
-        <v>25114</v>
+        <v>14439</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>20579191</t>
+          <t>1617942139</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20579191</t>
+          <t>https://m.place.naver.com/place/1617942139</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2256,29 +2248,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>와이오유 헤어 분당점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>songok82@naver.com</t>
-        </is>
-      </c>
+          <t>준오헤어 가든서현역점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1370-0256</t>
+          <t>0507-1497-0608</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로 100 정자 아이파크 1층</t>
+          <t>경기도 성남시 분당구 분당로53번길 20 이랜드프라자 3층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/y.o.u_salon</t>
+          <t>http://www.instagram.com/juno_garden_sh</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2313,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>10937</v>
+        <v>27651</v>
       </c>
       <c r="Q20" t="n">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="R20" t="n">
-        <v>11442</v>
+        <v>28201</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2328,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1661978943</t>
+          <t>34259267</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661978943</t>
+          <t>https://m.place.naver.com/place/34259267</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2350,29 +2338,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>요미앤디 분당정자역점</t>
+          <t>아이엠헤어 본점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rjvhseih@naver.com</t>
+          <t>cloud15000@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1433-0157</t>
+          <t>0507-1344-2326</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로232번길 25 위브제니스 B동 101호 요미앤디</t>
+          <t>경기도 성남시 분당구 백현로101번길 16 대덕프라자 2층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yomind_official</t>
+          <t>https://blog.naver.com/cloud15000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2387,7 +2375,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2407,13 +2395,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7210</v>
+        <v>9339</v>
       </c>
       <c r="Q21" t="n">
-        <v>3106</v>
+        <v>1016</v>
       </c>
       <c r="R21" t="n">
-        <v>10316</v>
+        <v>10355</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2422,17 +2410,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1783088941</t>
+          <t>1701957602</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1783088941</t>
+          <t>https://m.place.naver.com/place/1701957602</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2444,29 +2432,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>리미띠에헤어 분당판교점</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>limitie22@naver.com</t>
-        </is>
-      </c>
+          <t>퓨어유헤어 분당정자역점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1408-2150</t>
+          <t>0507-1477-0352</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층</t>
+          <t>경기도 성남시 분당구 정자일로 192 2층 202호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/limitie_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2476,7 +2460,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2497,17 +2481,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2092</v>
+        <v>1429</v>
       </c>
       <c r="Q22" t="n">
-        <v>4710</v>
+        <v>4014</v>
       </c>
       <c r="R22" t="n">
-        <v>6802</v>
+        <v>5443</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2516,17 +2500,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1490723364</t>
+          <t>1118386480</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490723364</t>
+          <t>https://m.place.naver.com/place/1118386480</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2538,29 +2522,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>리수헤어 미금역2호점</t>
+          <t>아이디헤어 분당수내점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bluesoyee95@naver.com</t>
+          <t>idhairsunae@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1346-0710</t>
+          <t>0507-1407-0805</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 미금프라자 3층 301호</t>
+          <t>경기도 성남시 분당구 백현로101번길 21 풍해빌딩 2층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/lisu_hair</t>
+          <t>https://blog.naver.com/idhairsunae</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2575,7 +2559,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2595,13 +2579,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>858</v>
+        <v>17360</v>
       </c>
       <c r="Q23" t="n">
-        <v>268</v>
+        <v>1035</v>
       </c>
       <c r="R23" t="n">
-        <v>1126</v>
+        <v>18395</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2610,17 +2594,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2076373994</t>
+          <t>35240005</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076373994</t>
+          <t>https://m.place.naver.com/place/35240005</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2632,29 +2616,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>헤리안</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>berrytaste@naver.com</t>
-        </is>
-      </c>
+          <t>리수헤어 미금역 본점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1381-7970</t>
+          <t>0507-1490-6066</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 235 N동 1층 129호</t>
+          <t>경기도 성남시 분당구 성남대로 151 엠코헤리츠 2층 207, 207-1호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/herian_official</t>
+          <t>https://www.instagram.com/lisu_hair</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2689,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>573</v>
+        <v>10240</v>
       </c>
       <c r="Q24" t="n">
-        <v>170</v>
+        <v>1576</v>
       </c>
       <c r="R24" t="n">
-        <v>743</v>
+        <v>11816</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2704,17 +2684,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1327869349</t>
+          <t>1876888147</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327869349</t>
+          <t>https://m.place.naver.com/place/1876888147</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2726,29 +2706,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>그로잉살롱 분당수내점</t>
+          <t>차홍룸 분당점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dhtosh@naver.com</t>
+          <t>chahong1@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1349-2578</t>
+          <t>0507-1326-6218</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 20 3층 301호</t>
+          <t>경기도 성남시 분당구 성남대로 393 두산위브파빌리온 A동 2층 211호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dhtosh/223230661811</t>
+          <t>https://blog.naver.com/chahong1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2783,13 +2763,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>895</v>
+        <v>2930</v>
       </c>
       <c r="Q25" t="n">
-        <v>1175</v>
+        <v>231</v>
       </c>
       <c r="R25" t="n">
-        <v>2070</v>
+        <v>3161</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2798,17 +2778,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1562063800</t>
+          <t>2025341850</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1562063800</t>
+          <t>https://m.place.naver.com/place/2025341850</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2820,29 +2800,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>헤어다이아 분당미금스타점</t>
+          <t>에이치플레이스 그레이츠판교역점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>hairdia20@naver.com</t>
+          <t>woosy0225@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1317-0651</t>
+          <t>0507-1320-5923</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 67 2층 헤어다이아 분당미금스타점</t>
+          <t>경기도 성남시 분당구 분당내곡로 117 그레이츠 판교 2층 201-2호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hairdia_migeumstar</t>
+          <t>https://www.instagram.com/h.place_official</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2877,13 +2857,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>10601</v>
+        <v>6156</v>
       </c>
       <c r="Q26" t="n">
-        <v>2870</v>
+        <v>676</v>
       </c>
       <c r="R26" t="n">
-        <v>13471</v>
+        <v>6832</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2892,17 +2872,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1695597038</t>
+          <t>1774601367</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695597038</t>
+          <t>https://m.place.naver.com/place/1774601367</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2914,29 +2894,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>준오헤어 미금역1호점</t>
+          <t>토니앤가이 판교점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>juno_mg1@naver.com</t>
+          <t>hair121212@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>031-609-0605</t>
+          <t>031-703-7577</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 51 천사의도시2차 2층 준오헤어 미금역1호점</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교푸르지오월드마크 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/juno_mg1</t>
+          <t>https://blog.naver.com/hair121212</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2967,17 +2947,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>22189</v>
+        <v>4248</v>
       </c>
       <c r="Q27" t="n">
-        <v>2919</v>
+        <v>181</v>
       </c>
       <c r="R27" t="n">
-        <v>25108</v>
+        <v>4429</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2986,17 +2966,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37236552</t>
+          <t>1891585241</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37236552</t>
+          <t>https://m.place.naver.com/place/1891585241</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3008,29 +2988,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>제니스튜디오 수내점</t>
+          <t>준오헤어 수내역1호점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sophia_nyj@naver.com</t>
+          <t>junosunae_1@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1390-4856</t>
+          <t>0507-1338-5605</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로 39 지웰 푸르지오 2층 224호 제니스튜디오 수내점</t>
+          <t>경기도 성남시 분당구 백현로101번길 22 성남농협 2F</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/junohair_sunae1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3040,7 +3020,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3061,17 +3041,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1200</v>
+        <v>15969</v>
       </c>
       <c r="Q28" t="n">
-        <v>612</v>
+        <v>559</v>
       </c>
       <c r="R28" t="n">
-        <v>1812</v>
+        <v>16528</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3080,17 +3060,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>37086276</t>
+          <t>11726571</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37086276</t>
+          <t>https://m.place.naver.com/place/11726571</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3102,29 +3082,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 분당정자점</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>adorable630@naver.com</t>
-        </is>
-      </c>
+          <t>꾸밈 미금역점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1349-0671</t>
+          <t>031-607-5362</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 234 태남프라자 203호</t>
+          <t>경기도 성남시 분당구 돌마로 47 이코노샤르망 4층 407호 꾸밈 미금역점</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/psc_jeongja</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3134,7 +3110,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3155,17 +3131,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3648</v>
+        <v>2179</v>
       </c>
       <c r="Q29" t="n">
-        <v>242</v>
+        <v>3910</v>
       </c>
       <c r="R29" t="n">
-        <v>3890</v>
+        <v>6089</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3174,17 +3150,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>12774906</t>
+          <t>1487844528</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12774906</t>
+          <t>https://m.place.naver.com/place/1487844528</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3196,29 +3172,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아티스틱 판교점</t>
+          <t>준오헤어 판교아브뉴프랑점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sxbapribfn796@naver.com</t>
+          <t>dlwnsrl48@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1452-9191</t>
+          <t>0507-1496-5646</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 2층 아티스틱 판교점</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 2층 238호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artistichair_</t>
+          <t>https://www.instagram.com/juno_pangyoaf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3253,13 +3229,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2713</v>
+        <v>3443</v>
       </c>
       <c r="Q30" t="n">
-        <v>594</v>
+        <v>1435</v>
       </c>
       <c r="R30" t="n">
-        <v>3307</v>
+        <v>4878</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3268,17 +3244,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>37997378</t>
+          <t>2092451717</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37997378</t>
+          <t>https://m.place.naver.com/place/2092451717</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3290,29 +3266,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>궁서채 서현역점</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>muadhair@naver.com</t>
-        </is>
-      </c>
+          <t>토니앤가이 분당미금역점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1467-2069</t>
+          <t>0507-1365-8540</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로180번길 13 3층 302호 궁서채 서현역점</t>
+          <t>경기도 성남시 분당구 성남대로171번길 17 1층 105호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/muadhair</t>
+          <t>https://www.instagram.com/toni_guymigeum?igsh=cTdvc2tlYmFydDFs</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3327,7 +3299,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3343,17 +3315,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>401</v>
+        <v>6319</v>
       </c>
       <c r="Q31" t="n">
-        <v>1275</v>
+        <v>608</v>
       </c>
       <c r="R31" t="n">
-        <v>1676</v>
+        <v>6927</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3362,17 +3334,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1278312550</t>
+          <t>1716511301</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1278312550</t>
+          <t>https://m.place.naver.com/place/1716511301</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3384,29 +3356,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>준오헤어 판교아브뉴프랑점</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>dlwnsrl48@naver.com</t>
-        </is>
-      </c>
+          <t>박준뷰티랩 분당정자역점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1496-5646</t>
+          <t>0507-1302-4411</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 2층 238호</t>
+          <t>경기도 성남시 분당구 느티로 27 2층 201호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/juno_pangyoaf</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3416,7 +3384,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3437,17 +3405,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3258</v>
+        <v>4061</v>
       </c>
       <c r="Q32" t="n">
-        <v>1388</v>
+        <v>5091</v>
       </c>
       <c r="R32" t="n">
-        <v>4646</v>
+        <v>9152</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3456,17 +3424,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2092451717</t>
+          <t>1045730051</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2092451717</t>
+          <t>https://m.place.naver.com/place/1045730051</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3478,29 +3446,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>이가자헤어비스 동판교점</t>
+          <t>꾸밈 야탑2호점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>lkjdpg@naver.com</t>
+          <t>liberoart@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>031-8016-8322</t>
+          <t>0507-1314-0866</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 메가스페이스 2층</t>
+          <t>경기도 성남시 분당구 장미로 86 이코노샤르망 3층 304호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lkjdpg</t>
+          <t>http://www.instagram.com/ggumim_</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3515,7 +3483,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3531,17 +3499,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3520</v>
+        <v>18325</v>
       </c>
       <c r="Q33" t="n">
-        <v>367</v>
+        <v>2772</v>
       </c>
       <c r="R33" t="n">
-        <v>3887</v>
+        <v>21097</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3550,17 +3518,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>37171597</t>
+          <t>1904557637</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37171597</t>
+          <t>https://m.place.naver.com/place/1904557637</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3572,29 +3540,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>꾸밈 판교역점</t>
+          <t>유나헤어 미금점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jooa_design@naver.com</t>
+          <t>sunny7563@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>031-702-7700</t>
+          <t>0507-1406-0821</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 180 2층 201호 꾸밈 판교역점</t>
+          <t>경기도 성남시 분당구 미금로 251 성원상가 2층 206호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jooa_design</t>
+          <t>https://youtube.com/@u.na_hair</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3609,7 +3577,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3629,13 +3597,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3741</v>
+        <v>6412</v>
       </c>
       <c r="Q34" t="n">
-        <v>1705</v>
+        <v>879</v>
       </c>
       <c r="R34" t="n">
-        <v>5446</v>
+        <v>7291</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3644,17 +3612,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1107338199</t>
+          <t>1237584348</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107338199</t>
+          <t>https://m.place.naver.com/place/1237584348</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3666,29 +3634,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>로컬 서현역점</t>
+          <t>허지스헤어 야탑1호점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>b_abe_@naver.com</t>
+          <t>herzis@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>031-701-7177</t>
+          <t>0507-1351-0222</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 다두프라자 2층 207호</t>
+          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 2층 207호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/local_hw</t>
+          <t>https://www.instagram.com/herzis_official</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3723,13 +3691,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>868</v>
+        <v>5971</v>
       </c>
       <c r="Q35" t="n">
-        <v>2172</v>
+        <v>369</v>
       </c>
       <c r="R35" t="n">
-        <v>3040</v>
+        <v>6340</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3738,17 +3706,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1061384556</t>
+          <t>31351403</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061384556</t>
+          <t>https://m.place.naver.com/place/31351403</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3760,29 +3728,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>살롱고은</t>
+          <t>에이치레이블 분당미금역점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sotongqueen@naver.com</t>
+          <t>hlabelhair@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1308-6179</t>
+          <t>0507-1352-8540</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 2층 207호</t>
+          <t>경기도 성남시 분당구 돌마로90번길 4 2층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salon_goeun</t>
+          <t>https://blog.naver.com/hlabelhair</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3797,7 +3765,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3817,13 +3785,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2194</v>
+        <v>2983</v>
       </c>
       <c r="Q36" t="n">
-        <v>125</v>
+        <v>1490</v>
       </c>
       <c r="R36" t="n">
-        <v>2319</v>
+        <v>4473</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3832,17 +3800,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1507880480</t>
+          <t>1556900244</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1507880480</t>
+          <t>https://m.place.naver.com/place/1556900244</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3854,29 +3822,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>준오헤어 미금역2호점</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>mg28817@naver.com</t>
-        </is>
-      </c>
+          <t>와이오유 헤어 분당점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1372-0609</t>
+          <t>0507-1370-0256</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 75 미금프라자 2층</t>
+          <t>경기도 성남시 분당구 백현로 100 정자 아이파크 1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mg28817</t>
+          <t>http://www.instagram.com/y.o.u_salon</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3891,7 +3855,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3911,13 +3875,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>16610</v>
+        <v>10957</v>
       </c>
       <c r="Q37" t="n">
-        <v>1927</v>
+        <v>510</v>
       </c>
       <c r="R37" t="n">
-        <v>18537</v>
+        <v>11467</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3926,17 +3890,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>20753530</t>
+          <t>1661978943</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20753530</t>
+          <t>https://m.place.naver.com/place/1661978943</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3948,29 +3912,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>아이디헤어 분당수내점</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>idhairsunae@naver.com</t>
-        </is>
-      </c>
+          <t>브린헤어 야탑역점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1407-0805</t>
+          <t>0507-1360-6702</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 21 풍해빌딩 2층</t>
+          <t>경기도 성남시 분당구 성남대로916번길 11 글라스타워 2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/idhairsunae</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3980,12 +3940,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4001,17 +3961,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>17313</v>
+        <v>2967</v>
       </c>
       <c r="Q38" t="n">
-        <v>972</v>
+        <v>1916</v>
       </c>
       <c r="R38" t="n">
-        <v>18285</v>
+        <v>4883</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4020,17 +3980,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>35240005</t>
+          <t>1043188175</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35240005</t>
+          <t>https://m.place.naver.com/place/1043188175</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4042,34 +4002,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>비롬헤어 정자본점</t>
+          <t>온무드헤어디자인랩 분당정자점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>gpkjinycfa@naver.com</t>
+          <t>min_direct@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>031-711-4868</t>
+          <t>0507-1399-1209</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 제3층 306호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 백궁1프라자 508호 509호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCkg0OWuxAMmBk7275MWZiOg</t>
+          <t>https://www.instagram.com/onmood_hair</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4099,13 +4059,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4274</v>
+        <v>3420</v>
       </c>
       <c r="Q39" t="n">
-        <v>2582</v>
+        <v>1733</v>
       </c>
       <c r="R39" t="n">
-        <v>6856</v>
+        <v>5153</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4114,17 +4074,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1491452961</t>
+          <t>1701632716</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1491452961</t>
+          <t>https://m.place.naver.com/place/1701632716</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4136,29 +4096,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>비롬헤어 서현점</t>
+          <t>준오헤어 서현역2호점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>eungangii@naver.com</t>
+          <t>juno_seohyeon2@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1440-4868</t>
+          <t>031-704-0605</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 13 3층 303호</t>
+          <t>경기도 성남시 분당구 황새울로342번길 23 기영프라자 3층 준오헤어 서현역2호점</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/berom_hair</t>
+          <t>https://www.instagram.com/juno_seohyeon2_look</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4193,13 +4153,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>304</v>
+        <v>17673</v>
       </c>
       <c r="Q40" t="n">
-        <v>114</v>
+        <v>888</v>
       </c>
       <c r="R40" t="n">
-        <v>418</v>
+        <v>18561</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4208,17 +4168,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2015119606</t>
+          <t>11726588</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015119606</t>
+          <t>https://m.place.naver.com/place/11726588</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4230,29 +4190,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>리안헤어 서현역점</t>
+          <t>박승철헤어스투디오 서현역점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sam_box@naver.com</t>
+          <t>pscsh1234@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1366-5800</t>
+          <t>0507-1359-3031</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 16 유성트윈프라자1차 2층 201호</t>
+          <t>경기도 성남시 분당구 서현로210번길 14 301호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/pscsh1234</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4262,12 +4222,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4283,17 +4243,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3023</v>
+        <v>5287</v>
       </c>
       <c r="Q41" t="n">
-        <v>1820</v>
+        <v>2693</v>
       </c>
       <c r="R41" t="n">
-        <v>4843</v>
+        <v>7980</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4302,17 +4262,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1957266860</t>
+          <t>1545175978</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1957266860</t>
+          <t>https://m.place.naver.com/place/1545175978</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4324,34 +4284,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>에이치레이블 분당미금역점</t>
+          <t>블랭크유 정자역본점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hlabelhair@naver.com</t>
+          <t>beauty_go@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1352-8540</t>
+          <t>0507-1412-6655</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로90번길 4 2층</t>
+          <t>경기도 성남시 분당구 성남대로 349 시그마타워 2층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hlabelhair</t>
+          <t>http://pf.kakao.com/_BxfxevT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4361,7 +4321,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4372,7 +4332,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4381,13 +4341,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2971</v>
+        <v>8423</v>
       </c>
       <c r="Q42" t="n">
-        <v>1354</v>
+        <v>1495</v>
       </c>
       <c r="R42" t="n">
-        <v>4325</v>
+        <v>9918</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4396,17 +4356,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1556900244</t>
+          <t>37749349</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1556900244</t>
+          <t>https://m.place.naver.com/place/37749349</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4418,29 +4378,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>온무드헤어디자인랩 분당정자점</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>onmood_1@naver.com</t>
-        </is>
-      </c>
+          <t>박승철헤어스투디오 분당정자점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1399-1209</t>
+          <t>0507-1349-0671</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 백궁1프라자 508호 509호</t>
+          <t>경기도 성남시 분당구 정자일로 234 태남프라자 203호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onmood_hair</t>
+          <t>https://www.instagram.com/psc_jeongja</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4475,13 +4431,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3290</v>
+        <v>3724</v>
       </c>
       <c r="Q43" t="n">
-        <v>1622</v>
+        <v>244</v>
       </c>
       <c r="R43" t="n">
-        <v>4912</v>
+        <v>3968</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4490,17 +4446,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1701632716</t>
+          <t>12774906</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701632716</t>
+          <t>https://m.place.naver.com/place/12774906</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4512,29 +4468,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CHOP헤어 분당점</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>chop_bdjj@naver.com</t>
-        </is>
-      </c>
+          <t>이철헤어커커 분당미금역점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1424-9636</t>
+          <t>0507-1448-2328</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 345 305호 CHOP헤어 분당점</t>
+          <t>경기도 성남시 분당구 성남대로 151 엠코헤르츠 1층 107호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chop_bundang</t>
+          <t>https://www.instagram.com/kerker_migeum?igsh=Z280bmNzcG1nbHhr</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4569,13 +4521,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>6298</v>
+        <v>6279</v>
       </c>
       <c r="Q44" t="n">
-        <v>1691</v>
+        <v>957</v>
       </c>
       <c r="R44" t="n">
-        <v>7989</v>
+        <v>7236</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4584,17 +4536,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1305705196</t>
+          <t>168115048</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1305705196</t>
+          <t>https://m.place.naver.com/place/168115048</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4606,29 +4558,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>허지스헤어 야탑1호점</t>
+          <t>에이치플레이스 정자역점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>herzis@naver.com</t>
+          <t>hplace_jeongja@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1351-0222</t>
+          <t>0507-1481-0850</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 10 분당아미고타워 2층 207호</t>
+          <t>경기도 성남시 분당구 정자일로 135 D동 202호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/herzis_official</t>
+          <t>https://www.instagram.com/h.place_jeongja</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4663,13 +4615,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>5900</v>
+        <v>6115</v>
       </c>
       <c r="Q45" t="n">
-        <v>364</v>
+        <v>1361</v>
       </c>
       <c r="R45" t="n">
-        <v>6264</v>
+        <v>7476</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4678,17 +4630,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>31351403</t>
+          <t>1260848756</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31351403</t>
+          <t>https://m.place.naver.com/place/1260848756</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4700,29 +4652,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>디바이드 야탑점</t>
+          <t>더희수뷰티스토리 분당미금점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>skdhdh1230@naver.com</t>
+          <t>min-hye_0815@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1379-3039</t>
+          <t>0507-1356-1041</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 934 궁전 프라자2 5층 501호</t>
+          <t>경기도 성남시 분당구 성남대로 151 분당엠코헤리츠 1층 108,108-1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/divide_boss</t>
+          <t>https://blog.naver.com/min-hye_0815?tab=1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4737,7 +4689,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4757,13 +4709,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2348</v>
+        <v>7935</v>
       </c>
       <c r="Q46" t="n">
-        <v>770</v>
+        <v>298</v>
       </c>
       <c r="R46" t="n">
-        <v>3118</v>
+        <v>8233</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4772,17 +4724,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1772424787</t>
+          <t>1033534372</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772424787</t>
+          <t>https://m.place.naver.com/place/1033534372</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4794,29 +4746,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>공시하 판교점</t>
+          <t>이가자헤어비스 동판교점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>gongsiha@naver.com</t>
+          <t>lkjdpg@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1349-7513</t>
+          <t>031-8016-8322</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로1길 47 1층 공시하</t>
+          <t>경기도 성남시 분당구 판교로 375 메가스페이스 2층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gongsiha/223367774442</t>
+          <t>https://blog.naver.com/lkjdpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4847,17 +4799,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2444</v>
+        <v>3530</v>
       </c>
       <c r="Q47" t="n">
-        <v>3192</v>
+        <v>371</v>
       </c>
       <c r="R47" t="n">
-        <v>5636</v>
+        <v>3901</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4866,17 +4818,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1834367955</t>
+          <t>37171597</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1834367955</t>
+          <t>https://m.place.naver.com/place/37171597</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4888,29 +4840,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>리수헤어 미금역 본점</t>
+          <t>준오헤어 미금역1호점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>odeprecise@naver.com</t>
+          <t>juno_mg1@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1490-6066</t>
+          <t>031-609-0605</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 151 엠코헤리츠 2층 207, 207-1호</t>
+          <t>경기도 성남시 분당구 돌마로 51 천사의도시2차 2층 준오헤어 미금역1호점</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lisu_hair</t>
+          <t>https://blog.naver.com/juno_mg1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4925,7 +4877,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4945,13 +4897,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>10053</v>
+        <v>22315</v>
       </c>
       <c r="Q48" t="n">
-        <v>1538</v>
+        <v>2966</v>
       </c>
       <c r="R48" t="n">
-        <v>11591</v>
+        <v>25281</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4960,17 +4912,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1876888147</t>
+          <t>37236552</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876888147</t>
+          <t>https://m.place.naver.com/place/37236552</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4982,29 +4934,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>꾸밈 야탑2호점</t>
+          <t>아비엘헤어 분당수내역점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>liberoart@naver.com</t>
+          <t>abiellehair@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1314-0866</t>
+          <t>0507-1325-9398</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 장미로 86 이코노샤르망 3층 304호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 4층 404호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ggumim_</t>
+          <t>https://blog.naver.com/abiellehair</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5019,7 +4971,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5039,13 +4991,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>18230</v>
+        <v>661</v>
       </c>
       <c r="Q49" t="n">
-        <v>2724</v>
+        <v>74</v>
       </c>
       <c r="R49" t="n">
-        <v>20954</v>
+        <v>735</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5054,17 +5006,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1904557637</t>
+          <t>1371585879</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1904557637</t>
+          <t>https://m.place.naver.com/place/1371585879</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5076,29 +5028,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>미봉헤어 야탑점</t>
+          <t>헤어다이아 분당미금스타점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>pziniziq@naver.com</t>
+          <t>hairdia20@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1455-7404</t>
+          <t>0507-1317-0651</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 7 서일빌딩 6층 603호 미봉헤어</t>
+          <t>경기도 성남시 분당구 돌마로 67 2층 헤어다이아 분당미금스타점</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mibonghair_yatap</t>
+          <t>https://www.instagram.com/hairdia_migeumstar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5133,13 +5085,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2145</v>
+        <v>10767</v>
       </c>
       <c r="Q50" t="n">
-        <v>1060</v>
+        <v>2905</v>
       </c>
       <c r="R50" t="n">
-        <v>3205</v>
+        <v>13672</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5148,17 +5100,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1229121617</t>
+          <t>1695597038</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229121617</t>
+          <t>https://m.place.naver.com/place/1695597038</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5170,29 +5122,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>브린헤어 야탑역점</t>
+          <t>프리미엄이가자 NC백화점야탑점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>thgusdl2016@naver.com</t>
+          <t>lkjyatop@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1360-6702</t>
+          <t>0507-1469-8784</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 11 글라스타워 2층</t>
+          <t>경기도 성남시 분당구 야탑로81번길 11 지하2층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/lkjyatop</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5202,12 +5154,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5227,13 +5179,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2936</v>
+        <v>985</v>
       </c>
       <c r="Q51" t="n">
-        <v>1749</v>
+        <v>107</v>
       </c>
       <c r="R51" t="n">
-        <v>4685</v>
+        <v>1092</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5242,17 +5194,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1043188175</t>
+          <t>2041236918</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043188175</t>
+          <t>https://m.place.naver.com/place/2041236918</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5264,29 +5216,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>오뉴월헤어 분당서현점</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>toptopq@naver.com</t>
-        </is>
-      </c>
+          <t>오브앤미헤어 서현역점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1415-3447</t>
+          <t>0507-1345-2089</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 21 대정빌딩 2층 오뉴월헤어</t>
+          <t>경기도 성남시 분당구 황새울로 326 2층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/toptopq</t>
+          <t>https://www.instagram.com/ovnme_00</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5301,7 +5249,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5321,13 +5269,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>11581</v>
+        <v>8225</v>
       </c>
       <c r="Q52" t="n">
-        <v>852</v>
+        <v>785</v>
       </c>
       <c r="R52" t="n">
-        <v>12433</v>
+        <v>9010</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5336,17 +5284,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1335157831</t>
+          <t>1801434728</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335157831</t>
+          <t>https://m.place.naver.com/place/1801434728</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5358,29 +5306,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>미노크 판교 본점</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>day00ung@naver.com</t>
-        </is>
-      </c>
+          <t>비롬헤어 정자본점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1393-4669</t>
+          <t>031-711-4868</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로3길 18 1층 102호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1 제3층 306호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/menoke.official/?igshid=YmMyMTA2M2Y%3D</t>
+          <t>https://www.youtube.com/channel/UCkg0OWuxAMmBk7275MWZiOg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5415,13 +5359,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2181</v>
+        <v>4285</v>
       </c>
       <c r="Q53" t="n">
-        <v>141</v>
+        <v>2629</v>
       </c>
       <c r="R53" t="n">
-        <v>2322</v>
+        <v>6914</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5430,17 +5374,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1260361427</t>
+          <t>1491452961</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260361427</t>
+          <t>https://m.place.naver.com/place/1491452961</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5452,29 +5396,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>로이드밤 분당서현역점</t>
+          <t>메이원헤어 미금점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>della_s@naver.com</t>
+          <t>jjenny87@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1391-5611</t>
+          <t>0507-1368-0224</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 10 다두프라자 3층 302호</t>
+          <t>경기도 성남시 분당구 돌마로 52 MD프라자 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lloydbomb_seohyeon_official</t>
+          <t>https://www.instagram.com/may.onehair_mg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5509,13 +5453,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3975</v>
+        <v>6782</v>
       </c>
       <c r="Q54" t="n">
-        <v>1050</v>
+        <v>1844</v>
       </c>
       <c r="R54" t="n">
-        <v>5025</v>
+        <v>8626</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5524,17 +5468,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1517546324</t>
+          <t>1509347542</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517546324</t>
+          <t>https://m.place.naver.com/place/1509347542</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5546,34 +5490,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>룹헤어 야탑점</t>
+          <t>이가자헤어비스 분당이마트점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>somi_miso@naver.com</t>
+          <t>lkj01577@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1494-2412</t>
+          <t>0507-1405-1528</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로916번길 7 3층 305호 룹헤어</t>
+          <t>경기도 성남시 분당구 불정로 134 이마트 3층 이가자헤어비스</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://naver.me/5oExpy79</t>
+          <t>https://blog.naver.com/lkj01577</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5583,7 +5527,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5599,17 +5543,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1384</v>
+        <v>10738</v>
       </c>
       <c r="Q55" t="n">
-        <v>649</v>
+        <v>870</v>
       </c>
       <c r="R55" t="n">
-        <v>2033</v>
+        <v>11608</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5618,17 +5562,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1146628079</t>
+          <t>12960329</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1146628079</t>
+          <t>https://m.place.naver.com/place/12960329</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5640,29 +5584,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>원바이원살롱 분당서현점</t>
+          <t>준오헤어 수내역2호점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>onebyone_salon@naver.com</t>
+          <t>c2162131@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1386-0421</t>
+          <t>0507-1487-0605</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 12 나산프라자 2층 203호</t>
+          <t>경기도 성남시 분당구 백현로 97 다운타운 3층 준오헤어 수내역2호점</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onebyone_salon/</t>
+          <t>https://blog.naver.com/c2162131</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5677,7 +5621,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5697,13 +5641,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1981</v>
+        <v>14898</v>
       </c>
       <c r="Q56" t="n">
-        <v>722</v>
+        <v>3683</v>
       </c>
       <c r="R56" t="n">
-        <v>2703</v>
+        <v>18581</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5712,17 +5656,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1595583709</t>
+          <t>34919368</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1595583709</t>
+          <t>https://m.place.naver.com/place/34919368</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5734,29 +5678,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>준오헤어 수내역2호점</t>
+          <t>리미띠에헤어 분당판교점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>c2162131@naver.com</t>
+          <t>limitie22@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1487-0605</t>
+          <t>0507-1408-2150</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로 97 다운타운 3층 준오헤어 수내역2호점</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/c2162131</t>
+          <t>https://www.instagram.com/limitie_/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5771,7 +5715,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5791,13 +5735,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>14820</v>
+        <v>2115</v>
       </c>
       <c r="Q57" t="n">
-        <v>3614</v>
+        <v>4853</v>
       </c>
       <c r="R57" t="n">
-        <v>18434</v>
+        <v>6968</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5806,17 +5750,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>34919368</t>
+          <t>1490723364</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34919368</t>
+          <t>https://m.place.naver.com/place/1490723364</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5828,29 +5772,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>미봉헤어 서현점</t>
+          <t>헤어더뷰 서현점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>good_jh91@naver.com</t>
+          <t>fbgid1023@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1364-9386</t>
+          <t>0507-1332-5008</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 26 3층 미봉헤어 서현점</t>
+          <t>경기도 성남시 분당구 분당로53번길 14 서현프라자 3층 303호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/mrbonghair_ceo</t>
+          <t>https://www.instagram.com/hairthebeau_sh</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5885,13 +5829,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1599</v>
+        <v>5216</v>
       </c>
       <c r="Q58" t="n">
-        <v>329</v>
+        <v>941</v>
       </c>
       <c r="R58" t="n">
-        <v>1928</v>
+        <v>6157</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5900,17 +5844,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>446940513</t>
+          <t>1912076517</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/446940513</t>
+          <t>https://m.place.naver.com/place/1912076517</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5922,29 +5866,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>예움헤어 분당정자점</t>
+          <t>준오헤어 서판교점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>yewoom4@naver.com</t>
+          <t>lailaixien@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1484-4886</t>
+          <t>0507-1332-0610</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 13 백궁프라자1차 4층 예움헤어 분당</t>
+          <t>경기도 성남시 분당구 운중로 249 더제이에스빌딩 2층 준오헤어 서판교점</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yewoom4</t>
+          <t>https://www.instagram.com/junospg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5959,7 +5903,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5979,13 +5923,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2466</v>
+        <v>13082</v>
       </c>
       <c r="Q59" t="n">
-        <v>2573</v>
+        <v>480</v>
       </c>
       <c r="R59" t="n">
-        <v>5039</v>
+        <v>13562</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5994,17 +5938,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1682545825</t>
+          <t>1391913826</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682545825</t>
+          <t>https://m.place.naver.com/place/1391913826</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6016,29 +5960,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>아비엘헤어 분당수내역점</t>
+          <t>비롬헤어 서현점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>abiellehair@naver.com</t>
+          <t>ooooofus@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1325-9398</t>
+          <t>0507-1440-4868</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 32 코리아나빌딩 4층 404호</t>
+          <t>경기도 성남시 분당구 분당로53번길 13 3층 303호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/abiellehair</t>
+          <t>https://www.instagram.com/berom_hair</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6053,7 +5997,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6073,13 +6017,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>646</v>
+        <v>325</v>
       </c>
       <c r="Q60" t="n">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="R60" t="n">
-        <v>720</v>
+        <v>487</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6088,17 +6032,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1371585879</t>
+          <t>2015119606</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1371585879</t>
+          <t>https://m.place.naver.com/place/2015119606</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6110,34 +6054,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>유나헤어 미금점</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>sunny7563@naver.com</t>
-        </is>
-      </c>
+          <t>로이드밤 분당서현역점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1406-0821</t>
+          <t>0507-1391-5611</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 미금로 251 성원상가 2층 206호</t>
+          <t>경기도 성남시 분당구 서현로210번길 10 다두프라자 3층 302호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://youtube.com/@u.na_hair</t>
+          <t>https://www.instagram.com/lloydbomb_seohyeon_official</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6167,13 +6107,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>6366</v>
+        <v>4011</v>
       </c>
       <c r="Q61" t="n">
-        <v>620</v>
+        <v>1090</v>
       </c>
       <c r="R61" t="n">
-        <v>6986</v>
+        <v>5101</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6182,17 +6122,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1237584348</t>
+          <t>1517546324</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237584348</t>
+          <t>https://m.place.naver.com/place/1517546324</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6261,13 +6201,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>18714</v>
+        <v>18801</v>
       </c>
       <c r="Q62" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="R62" t="n">
-        <v>18933</v>
+        <v>19031</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6286,7 +6226,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6298,33 +6238,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>디엔헤어</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>hair_baraem2@naver.com</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>cto@handsos.com</t>
-        </is>
-      </c>
+          <t>준오헤어 판교알파돔시티점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1402-8483</t>
+          <t>0507-1389-0611</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로360번길 21 신영팰리스타워 201호</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔타워 3층 준오헤어</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/52036</t>
+          <t>http://junohair.com/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6334,12 +6266,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6359,13 +6291,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>4387</v>
+        <v>33696</v>
       </c>
       <c r="Q63" t="n">
-        <v>2371</v>
+        <v>1373</v>
       </c>
       <c r="R63" t="n">
-        <v>6758</v>
+        <v>35069</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6374,17 +6306,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>21399147</t>
+          <t>1377606557</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21399147</t>
+          <t>https://m.place.naver.com/place/1377606557</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6396,39 +6328,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>헤어더뷰 서현점</t>
+          <t>이가자헤어비스 이천일아울렛미금점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>fbgid1023@naver.com</t>
+          <t>lkjmk2001@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1332-5008</t>
+          <t>0507-1308-2899</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 14 서현프라자 3층 303호</t>
+          <t>경기도 성남시 분당구 미금일로154번길 20 2001아울렛 분당점 6층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hairthebeau_sh</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6453,13 +6385,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>5216</v>
+        <v>5337</v>
       </c>
       <c r="Q64" t="n">
-        <v>928</v>
+        <v>1918</v>
       </c>
       <c r="R64" t="n">
-        <v>6144</v>
+        <v>7255</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6468,17 +6400,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1912076517</t>
+          <t>30889274</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912076517</t>
+          <t>https://m.place.naver.com/place/30889274</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6449,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6547,13 +6479,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>331</v>
+        <v>421</v>
       </c>
       <c r="Q65" t="n">
-        <v>286</v>
+        <v>572</v>
       </c>
       <c r="R65" t="n">
-        <v>617</v>
+        <v>993</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6572,7 +6504,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6584,29 +6516,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 서현역점</t>
+          <t>Hair Seed194 수내역점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>pscsh1234@naver.com</t>
+          <t>seed194@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1359-3031</t>
+          <t>0507-1469-0195</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로210번길 14 301호</t>
+          <t>경기도 성남시 분당구 백현로101번길 16 대덕프라자 316호 Hair Seed194</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pscsh1234</t>
+          <t>https://blog.naver.com/seed194</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6641,13 +6573,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>5215</v>
+        <v>1784</v>
       </c>
       <c r="Q66" t="n">
-        <v>2980</v>
+        <v>1362</v>
       </c>
       <c r="R66" t="n">
-        <v>8195</v>
+        <v>3146</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6656,17 +6588,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1545175978</t>
+          <t>1993118007</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545175978</t>
+          <t>https://m.place.naver.com/place/1993118007</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6678,29 +6610,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>제니스튜디오 판교점</t>
+          <t>로컬 서현역점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>dkyun22@naver.com</t>
+          <t>b_abe_@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1385-8458</t>
+          <t>031-701-7177</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로10번길 10-4 1층</t>
+          <t>경기도 성남시 분당구 서현로210번길 10 다두프라자 2층 207호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dkyun22</t>
+          <t>https://www.instagram.com/local_hw</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6715,7 +6647,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6735,13 +6667,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2345</v>
+        <v>898</v>
       </c>
       <c r="Q67" t="n">
-        <v>772</v>
+        <v>2227</v>
       </c>
       <c r="R67" t="n">
-        <v>3117</v>
+        <v>3125</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6750,17 +6682,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1480897275</t>
+          <t>1061384556</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1480897275</t>
+          <t>https://m.place.naver.com/place/1061384556</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6772,29 +6704,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>동경하다 분당본점</t>
+          <t>어반트랜드 서현역 본점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ehdrud2019@naver.com</t>
+          <t>ohkong82@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1395-2232</t>
+          <t>0507-1400-5082</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 방아로 21 1층 동경하다</t>
+          <t>경기도 성남시 분당구 황새울로360번길 28 4층 401호, 402호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ehdrud2019</t>
+          <t>https://www.instagram.com/urbantrend_hair/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6809,7 +6741,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6829,13 +6761,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2342</v>
+        <v>22229</v>
       </c>
       <c r="Q68" t="n">
-        <v>129</v>
+        <v>3050</v>
       </c>
       <c r="R68" t="n">
-        <v>2471</v>
+        <v>25279</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6844,17 +6776,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1175950598</t>
+          <t>20579191</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1175950598</t>
+          <t>https://m.place.naver.com/place/20579191</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6866,29 +6798,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>박준뷰티랩 분당정자역점</t>
+          <t>궁서채 서현역점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>herahera@naver.com</t>
+          <t>muadhair@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1302-4411</t>
+          <t>0507-1467-2069</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 27 2층 201호</t>
+          <t>경기도 성남시 분당구 서현로180번길 13 3층 302호 궁서채 서현역점</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/muadhair</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6898,12 +6830,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6923,13 +6855,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>4060</v>
+        <v>409</v>
       </c>
       <c r="Q69" t="n">
-        <v>5070</v>
+        <v>1335</v>
       </c>
       <c r="R69" t="n">
-        <v>9130</v>
+        <v>1744</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6938,17 +6870,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1045730051</t>
+          <t>1278312550</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045730051</t>
+          <t>https://m.place.naver.com/place/1278312550</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6960,29 +6892,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>차홍룸 판교점</t>
+          <t>아우드헤어 정자역점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>chahong1@naver.com</t>
+          <t>gkhacker@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1337-4752</t>
+          <t>0507-1369-9947</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 상가1층 1105호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 젤존타워3 4층 407호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/chahongofficial</t>
+          <t>https://www.instagram.com/ouudhair</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6997,7 +6929,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7017,13 +6949,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>13854</v>
+        <v>503</v>
       </c>
       <c r="Q70" t="n">
-        <v>298</v>
+        <v>215</v>
       </c>
       <c r="R70" t="n">
-        <v>14152</v>
+        <v>718</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7032,17 +6964,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1617942139</t>
+          <t>2077539595</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1617942139</t>
+          <t>https://m.place.naver.com/place/2077539595</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7054,29 +6986,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>프리미엄이가자 NC백화점야탑점</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>lkjyatop@naver.com</t>
-        </is>
-      </c>
+          <t>살롱고은</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1469-8784</t>
+          <t>0507-1308-6179</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로81번길 11 지하2층</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 2층 207호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lkjyatop</t>
+          <t>https://www.instagram.com/salon_goeun</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7091,7 +7019,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7107,17 +7035,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>873</v>
+        <v>2223</v>
       </c>
       <c r="Q71" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="R71" t="n">
-        <v>973</v>
+        <v>2356</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7126,17 +7054,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2041236918</t>
+          <t>1507880480</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041236918</t>
+          <t>https://m.place.naver.com/place/1507880480</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7148,29 +7076,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>꾸밈 야탑본점</t>
+          <t>리안헤어 서현역점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>liberoart@naver.com</t>
+          <t>sam_box@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1402-0850</t>
+          <t>0507-1366-5800</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로926번길 6 야탑 대덕프라자 304호</t>
+          <t>경기도 성남시 분당구 서현로210번길 16 유성트윈프라자1차 2층 201호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ggumim_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7180,7 +7108,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7201,17 +7129,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>14258</v>
+        <v>3064</v>
       </c>
       <c r="Q72" t="n">
-        <v>3099</v>
+        <v>1859</v>
       </c>
       <c r="R72" t="n">
-        <v>17357</v>
+        <v>4923</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7220,17 +7148,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>36424132</t>
+          <t>1957266860</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36424132</t>
+          <t>https://m.place.naver.com/place/1957266860</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7242,29 +7170,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>퓨어유헤어 분당정자역점</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>tmi_world@naver.com</t>
-        </is>
-      </c>
+          <t>와이오유 판교점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1477-0352</t>
+          <t>0507-1406-1479</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 192 2층 202호</t>
+          <t>경기도 성남시 분당구 판교역로18번길 18</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.youtube.com/c/와이오유yousalon</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7274,7 +7198,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7295,17 +7219,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1397</v>
+        <v>10115</v>
       </c>
       <c r="Q73" t="n">
-        <v>3969</v>
+        <v>811</v>
       </c>
       <c r="R73" t="n">
-        <v>5366</v>
+        <v>10926</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7314,17 +7238,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1118386480</t>
+          <t>35194802</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118386480</t>
+          <t>https://m.place.naver.com/place/35194802</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7336,34 +7260,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>준오헤어 판교알파돔시티점</t>
+          <t>아이엠헤어 정자점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>junopg0605@naver.com</t>
+          <t>cloud15000@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1389-0611</t>
+          <t>0507-1478-0803</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔타워 3층 준오헤어</t>
+          <t>경기도 성남시 분당구 정자일로 240 월드프라자 2층 204호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://junohair.com/</t>
+          <t>https://www.instagram.com/im.hair_/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7393,13 +7317,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>33583</v>
+        <v>2578</v>
       </c>
       <c r="Q74" t="n">
-        <v>1369</v>
+        <v>234</v>
       </c>
       <c r="R74" t="n">
-        <v>34952</v>
+        <v>2812</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7408,17 +7332,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1377606557</t>
+          <t>1147513414</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377606557</t>
+          <t>https://m.place.naver.com/place/1147513414</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7430,29 +7354,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>345헤어살롱 미금점</t>
+          <t>꼼나나비앙 판교점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>fifaking@naver.com</t>
+          <t>comme_pangyo@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>031-712-0345</t>
+          <t>0507-1332-8195</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 돌마로 85 하나은행 3층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 10 라스트리트 1동 2층 224호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fifaking</t>
+          <t>https://www.instagram.com/commenanabien_pangyo/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7467,7 +7391,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7483,17 +7407,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>4288</v>
+        <v>5973</v>
       </c>
       <c r="Q75" t="n">
-        <v>1436</v>
+        <v>379</v>
       </c>
       <c r="R75" t="n">
-        <v>5724</v>
+        <v>6352</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7502,51 +7426,51 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>514443180</t>
+          <t>1867649955</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/514443180</t>
+          <t>https://m.place.naver.com/place/1867649955</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>덕테일 바버샵</t>
+          <t>꾸밈 판교역점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>amorsino@naver.com</t>
+          <t>jooa_design@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1397-4798</t>
+          <t>031-702-7700</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 34 1층</t>
+          <t>경기도 성남시 분당구 판교역로 180 2층 201호 꾸밈 판교역점</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jooa_design</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7556,12 +7480,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7577,17 +7501,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1313</v>
+        <v>3785</v>
       </c>
       <c r="Q76" t="n">
-        <v>180</v>
+        <v>1840</v>
       </c>
       <c r="R76" t="n">
-        <v>1493</v>
+        <v>5625</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7596,17 +7520,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1086675542</t>
+          <t>1107338199</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1086675542</t>
+          <t>https://m.place.naver.com/place/1107338199</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
